--- a/assets/constructions/examples/ctd_tsmb_tupleradial_fullround.xlsx
+++ b/assets/constructions/examples/ctd_tsmb_tupleradial_fullround.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH6"/>
+  <dimension ref="A1:AM6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,11 +599,36 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10.0SIR1.4MD7993-2.9VMX</t>
+          <t>6.0SIR1.1MD7993-1.3VMX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -629,37 +654,37 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>10.4</v>
+        <v>6.1</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="L2" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="O2" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="R2" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -668,7 +693,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>VARGUS_10SI02</t>
+          <t>VARGUS_6SI02</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -705,11 +730,22 @@
           <t>Full MAIN VARDEX 2022-METRIC.pdf</t>
         </is>
       </c>
+      <c r="AI2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6.0SIR1.0MD7993-1.2VMX</t>
+          <t>8.0SIR1.4MD7993-2.0VMX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -735,37 +771,37 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6.1</v>
+        <v>8.4</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O3" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -774,7 +810,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>VARGUS_6SI02</t>
+          <t>VARGUS_8SI02</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -811,11 +847,30 @@
           <t>Full MAIN VARDEX 2022-METRIC.pdf</t>
         </is>
       </c>
+      <c r="AI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>115.84</v>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AL3" t="n">
+        <v>10180.32</v>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6.0SIR1.1LD7993-1.3VMX</t>
+          <t>6.0SIR1.1SD7993-1.3VMX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -855,10 +910,10 @@
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="O4" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
@@ -917,11 +972,30 @@
           <t>Full MAIN VARDEX 2022-METRIC.pdf</t>
         </is>
       </c>
+      <c r="AI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>62.62</v>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AL4" t="n">
+        <v>5503.21</v>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6.0SIR1.0LD7993-1.2VMX</t>
+          <t>10.0SIR1.8MD7993-2.9VMX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -947,37 +1021,37 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6.1</v>
+        <v>10.4</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="O5" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -986,7 +1060,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>VARGUS_6SI02</t>
+          <t>VARGUS_10SI02</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1023,11 +1097,30 @@
           <t>Full MAIN VARDEX 2022-METRIC.pdf</t>
         </is>
       </c>
+      <c r="AI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>142.96</v>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AL5" t="n">
+        <v>12563.7</v>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8.0SIR1.4MD7993-2.0VMX</t>
+          <t>6.0SIR1.0SD7993-1.2VMX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1053,37 +1146,37 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8.4</v>
+        <v>6.1</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R6" t="n">
         <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.8</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1092,7 +1185,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>VARGUS_8SI02</t>
+          <t>VARGUS_6SI02</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1127,6 +1220,25 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Full MAIN VARDEX 2022-METRIC.pdf</t>
+        </is>
+      </c>
+      <c r="AI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>62.62</v>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AL6" t="n">
+        <v>5503.21</v>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
